--- a/Confiles/协议/读地址.xlsx
+++ b/Confiles/协议/读地址.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\空压机\Confiles\协议\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\code\真空罐压缩机\Confiles\协议\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{225C426D-CAA0-4CE9-85D4-8873B3BCEF06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD6E6D76-3FAD-49D7-9E59-845434544276}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -128,16 +128,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -145,26 +145,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -473,145 +474,155 @@
   <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.81640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.54296875" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.453125" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.81640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.7265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.54296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.7265625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="55.54296875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="6">
         <v>15</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="6">
         <v>540</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="6">
         <v>2</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="G2" s="7"/>
     </row>
     <row r="3" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="6">
         <v>4</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="6">
         <v>6</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="6">
         <v>2</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="G3" s="7"/>
     </row>
     <row r="4" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="6">
         <v>15</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="6">
         <v>142</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="6">
         <v>4</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="3" t="s">
         <v>13</v>
       </c>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
     </row>
     <row r="5" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="6">
         <v>15</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="6">
         <v>250</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="6">
         <v>4</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="3" t="s">
         <v>13</v>
       </c>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
     </row>
     <row r="6" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="6">
         <v>18</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="6">
         <v>562</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="6">
         <v>4</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="3" t="s">
         <v>13</v>
       </c>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
     </row>
     <row r="7" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="6">
         <v>15</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="6">
         <v>502</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="6">
         <v>4</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="3" t="s">
         <v>13</v>
       </c>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Confiles/协议/读地址.xlsx
+++ b/Confiles/协议/读地址.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\code\真空罐压缩机\Confiles\协议\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD6E6D76-3FAD-49D7-9E59-845434544276}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DBBEEF1-0211-4747-A59D-BE8A2C84C506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
   <si>
     <t>数据名称</t>
   </si>
@@ -46,9 +46,6 @@
     <t>bool</t>
   </si>
   <si>
-    <t>True:上电;False:断电;</t>
-  </si>
-  <si>
     <t>温控状态</t>
   </si>
   <si>
@@ -58,15 +55,9 @@
     <t>0:温控停止;1:温控运行;2:温控故障;</t>
   </si>
   <si>
-    <t>热沉当前设定温度</t>
-  </si>
-  <si>
     <t>real</t>
   </si>
   <si>
-    <t>热沉控温点温度</t>
-  </si>
-  <si>
     <t>冷板当前设定温度</t>
   </si>
   <si>
@@ -74,6 +65,182 @@
   </si>
   <si>
     <t>一体机上电标志</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>控温点当前设定温度</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>控温点温度</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>温控模式</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>bool</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>:定值;2:程序;</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>True:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>上电</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>;False:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>断电</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>True:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>热沉</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>;False:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>产品</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>True:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>均值</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>;False:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单点</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>温控点类型</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>温控类型</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -81,7 +248,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -106,6 +273,20 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
       <family val="2"/>
       <charset val="134"/>
     </font>
@@ -145,7 +326,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -156,16 +337,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -471,7 +645,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.81640625" style="1" bestFit="1" customWidth="1"/>
@@ -487,13 +661,13 @@
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="3" t="s">
@@ -507,122 +681,185 @@
       </c>
     </row>
     <row r="2" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" s="6">
+      <c r="A2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="3">
         <v>15</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="3">
         <v>540</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="3">
         <v>2</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" s="7"/>
+        <v>21</v>
+      </c>
+      <c r="G2" s="3"/>
     </row>
     <row r="3" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="3">
+        <v>4</v>
+      </c>
+      <c r="C3" s="3">
+        <v>6</v>
+      </c>
+      <c r="D3" s="3">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="6">
-        <v>4</v>
-      </c>
-      <c r="C3" s="6">
-        <v>6</v>
-      </c>
-      <c r="D3" s="6">
+      <c r="F3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="3"/>
+    </row>
+    <row r="4" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="3">
+        <v>15</v>
+      </c>
+      <c r="C4" s="3">
+        <v>470.1</v>
+      </c>
+      <c r="D4" s="3">
         <v>2</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="7"/>
-    </row>
-    <row r="4" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="6">
+      <c r="E4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="3"/>
+    </row>
+    <row r="5" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="3">
         <v>15</v>
       </c>
-      <c r="C4" s="6">
-        <v>142</v>
-      </c>
-      <c r="D4" s="6">
-        <v>4</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-    </row>
-    <row r="5" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="6">
-        <v>15</v>
-      </c>
-      <c r="C5" s="6">
-        <v>250</v>
-      </c>
-      <c r="D5" s="6">
-        <v>4</v>
+      <c r="C5" s="3">
+        <v>462</v>
+      </c>
+      <c r="D5" s="3">
+        <v>2</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
+        <v>18</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="3"/>
     </row>
     <row r="6" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="3">
         <v>15</v>
       </c>
-      <c r="B6" s="6">
+      <c r="C6" s="3">
+        <v>126</v>
+      </c>
+      <c r="D6" s="3">
+        <v>2</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" s="3"/>
+    </row>
+    <row r="7" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="3">
+        <v>15</v>
+      </c>
+      <c r="C7" s="3">
+        <v>142</v>
+      </c>
+      <c r="D7" s="3">
+        <v>4</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+    </row>
+    <row r="8" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="3">
+        <v>15</v>
+      </c>
+      <c r="C8" s="3">
+        <v>250</v>
+      </c>
+      <c r="D8" s="3">
+        <v>4</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+    </row>
+    <row r="9" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="3">
         <v>18</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C9" s="3">
         <v>562</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D9" s="3">
         <v>4</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+    </row>
+    <row r="10" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-    </row>
-    <row r="7" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="6">
+      <c r="B10" s="3">
         <v>15</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C10" s="3">
         <v>502</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D10" s="3">
         <v>4</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
+      <c r="E10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
